--- a/trade-elasticities-cointegration/outputs/section_11_econometric_models.xlsx
+++ b/trade-elasticities-cointegration/outputs/section_11_econometric_models.xlsx
@@ -22,7 +22,8 @@
     <sheet name="structural_dummies" sheetId="13" r:id="rId13"/>
     <sheet name="economic_interpretation_summary" sheetId="14" r:id="rId14"/>
     <sheet name="expected_signs_check" sheetId="15" r:id="rId15"/>
-    <sheet name="ecm_adjustment" sheetId="16" r:id="rId16"/>
+    <sheet name="literature_comparison_template" sheetId="16" r:id="rId16"/>
+    <sheet name="ecm_adjustment" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -414,7 +415,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -700,7 +701,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B11">
@@ -708,17 +709,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>l2_d_ln_pib_socios</t>
+          <t>l3_d_ln_itcrm</t>
         </is>
       </c>
       <c r="D11">
-        <v>0.9887398551778854</v>
+        <v>0.4502126691357331</v>
       </c>
       <c r="E11">
-        <v>-104.4724820290816</v>
+        <v>-183.8345074896196</v>
       </c>
       <c r="F11">
-        <v>-108.7348818904436</v>
+        <v>-187.326214418691</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -727,7 +728,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B12">
@@ -735,17 +736,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>l2_d_ln_commodity_price_index</t>
+          <t>l4_d_ln_itcrm</t>
         </is>
       </c>
       <c r="D12">
-        <v>0.9798691276187241</v>
+        <v>0.4548019713854338</v>
       </c>
       <c r="E12">
-        <v>-108.7348818904436</v>
+        <v>-187.326214418691</v>
       </c>
       <c r="F12">
-        <v>-112.996684023446</v>
+        <v>-190.8475377746936</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -754,7 +755,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B13">
@@ -762,17 +763,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>l1_d_ln_pib_socios</t>
+          <t>global_crisis_dummy</t>
         </is>
       </c>
       <c r="D13">
-        <v>0.5994995577258543</v>
+        <v>0.330981029510802</v>
       </c>
       <c r="E13">
-        <v>-112.996684023446</v>
+        <v>-190.8475377746936</v>
       </c>
       <c r="F13">
-        <v>-116.8864615023244</v>
+        <v>-193.8791122979537</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -781,7 +782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B14">
@@ -789,17 +790,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>l1_d_ln_commodity_price_index</t>
+          <t>l1_d_ln_imports_real</t>
         </is>
       </c>
       <c r="D14">
-        <v>0.7435149298713133</v>
+        <v>0.2822176208063553</v>
       </c>
       <c r="E14">
-        <v>-116.8864615023244</v>
+        <v>-193.8791122979537</v>
       </c>
       <c r="F14">
-        <v>-121.0070664485833</v>
+        <v>-196.6625427057386</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -808,7 +809,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B15">
@@ -816,17 +817,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>global_crisis_dummy</t>
+          <t>l2_d_ln_imports_real</t>
         </is>
       </c>
       <c r="D15">
-        <v>0.5322830106230758</v>
+        <v>0.1810834423992249</v>
       </c>
       <c r="E15">
-        <v>-121.0070664485833</v>
+        <v>-196.6625427057386</v>
       </c>
       <c r="F15">
-        <v>-124.7616564640226</v>
+        <v>-198.6776038477055</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -835,7 +836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B16">
@@ -847,13 +848,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.3804514657434359</v>
+        <v>0.2207014237410698</v>
       </c>
       <c r="E16">
-        <v>-124.7616564640226</v>
+        <v>-198.6776038477055</v>
       </c>
       <c r="F16">
-        <v>-128.0403104000273</v>
+        <v>-201.0884560336149</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -862,7 +863,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B17">
@@ -870,17 +871,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>l2_d_ln_itcrm</t>
+          <t>l3_d_ln_imports_real</t>
         </is>
       </c>
       <c r="D17">
-        <v>0.3048995545459032</v>
+        <v>0.152913957783842</v>
       </c>
       <c r="E17">
-        <v>-128.0403104000273</v>
+        <v>-201.0884560336149</v>
       </c>
       <c r="F17">
-        <v>-130.9802720465124</v>
+        <v>-202.8718237180915</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -889,7 +890,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B18">
@@ -901,13 +902,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.2394225337832592</v>
+        <v>0.1653644169452692</v>
       </c>
       <c r="E18">
-        <v>-130.9802720465124</v>
+        <v>-202.8718237180915</v>
       </c>
       <c r="F18">
-        <v>-133.5341185239602</v>
+        <v>-204.83820690964</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -916,7 +917,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B19">
@@ -924,17 +925,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>l3_d_ln_commodity_price_index</t>
+          <t>l3_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="D19">
-        <v>0.1119920453346879</v>
+        <v>0.2231181901385312</v>
       </c>
       <c r="E19">
-        <v>-133.5341185239602</v>
+        <v>-204.83820690964</v>
       </c>
       <c r="F19">
-        <v>-134.7314025049782</v>
+        <v>-207.3591845571713</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -947,21 +948,21 @@
         </is>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>l3_d_ln_itcrm</t>
+          <t>l2_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="D20">
-        <v>0.4502126691357331</v>
+        <v>0.2535693002241428</v>
       </c>
       <c r="E20">
-        <v>-183.8345074896196</v>
+        <v>-207.3591845571713</v>
       </c>
       <c r="F20">
-        <v>-187.326214418691</v>
+        <v>-210.1170466250611</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -974,21 +975,21 @@
         </is>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>l4_d_ln_itcrm</t>
+          <t>covid_dummy</t>
         </is>
       </c>
       <c r="D21">
-        <v>0.4548019713854338</v>
+        <v>0.3353877581453839</v>
       </c>
       <c r="E21">
-        <v>-187.326214418691</v>
+        <v>-210.1170466250611</v>
       </c>
       <c r="F21">
-        <v>-190.8475377746936</v>
+        <v>-213.3255827067548</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -997,25 +998,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>global_crisis_dummy</t>
+          <t>l2_d_ln_imports_real</t>
         </is>
       </c>
       <c r="D22">
-        <v>0.330981029510802</v>
+        <v>0.8771163692884485</v>
       </c>
       <c r="E22">
-        <v>-190.8475377746936</v>
+        <v>-188.1220575076477</v>
       </c>
       <c r="F22">
-        <v>-193.8791122979537</v>
+        <v>-192.3517768592431</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1024,25 +1025,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>l1_d_ln_imports_real</t>
+          <t>argentina_2018_dummy</t>
         </is>
       </c>
       <c r="D23">
-        <v>0.2822176208063553</v>
+        <v>0.9152478590682325</v>
       </c>
       <c r="E23">
-        <v>-193.8791122979537</v>
+        <v>-192.3517768592431</v>
       </c>
       <c r="F23">
-        <v>-196.6625427057386</v>
+        <v>-196.5991409669552</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1051,25 +1052,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>l2_d_ln_imports_real</t>
+          <t>l3_d_ln_itcrm</t>
         </is>
       </c>
       <c r="D24">
-        <v>0.1810834423992249</v>
+        <v>0.6779658854976038</v>
       </c>
       <c r="E24">
-        <v>-196.6625427057386</v>
+        <v>-196.5991409669552</v>
       </c>
       <c r="F24">
-        <v>-198.6776038477055</v>
+        <v>-200.6330061905594</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1078,25 +1079,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>argentina_2018_dummy</t>
+          <t>l3_d_ln_imports_real</t>
         </is>
       </c>
       <c r="D25">
-        <v>0.2207014237410698</v>
+        <v>0.5123934070021352</v>
       </c>
       <c r="E25">
-        <v>-198.6776038477055</v>
+        <v>-200.6330061905594</v>
       </c>
       <c r="F25">
-        <v>-201.0884560336149</v>
+        <v>-204.3366025602405</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1105,25 +1106,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>l3_d_ln_imports_real</t>
+          <t>l2_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="D26">
-        <v>0.152913957783842</v>
+        <v>0.3813353210222058</v>
       </c>
       <c r="E26">
-        <v>-201.0884560336149</v>
+        <v>-204.3366025602405</v>
       </c>
       <c r="F26">
-        <v>-202.8718237180915</v>
+        <v>-207.6189020879323</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1132,25 +1133,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>l1_d_ln_itcrm</t>
+          <t>covid_dummy</t>
         </is>
       </c>
       <c r="D27">
-        <v>0.1653644169452692</v>
+        <v>0.3518609645469802</v>
       </c>
       <c r="E27">
-        <v>-202.8718237180915</v>
+        <v>-207.6189020879323</v>
       </c>
       <c r="F27">
-        <v>-204.83820690964</v>
+        <v>-210.7924663088147</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1159,25 +1160,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>l3_d_ln_gdp_real</t>
+          <t>l4_d_ln_itcrm</t>
         </is>
       </c>
       <c r="D28">
-        <v>0.2231181901385312</v>
+        <v>0.2619346556913756</v>
       </c>
       <c r="E28">
-        <v>-204.83820690964</v>
+        <v>-210.7924663088147</v>
       </c>
       <c r="F28">
-        <v>-207.3591845571713</v>
+        <v>-213.5012520320983</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1186,25 +1187,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>l2_d_ln_gdp_real</t>
+          <t>global_crisis_dummy</t>
         </is>
       </c>
       <c r="D29">
-        <v>0.2535693002241428</v>
+        <v>0.1141610429150342</v>
       </c>
       <c r="E29">
-        <v>-207.3591845571713</v>
+        <v>-213.5012520320983</v>
       </c>
       <c r="F29">
-        <v>-210.1170466250611</v>
+        <v>-214.7352227707529</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1213,270 +1214,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>covid_dummy</t>
+          <t>l2_d_ln_itcrm</t>
         </is>
       </c>
       <c r="D30">
-        <v>0.3353877581453839</v>
+        <v>0.1070814546819217</v>
       </c>
       <c r="E30">
-        <v>-210.1170466250611</v>
+        <v>-214.7352227707529</v>
       </c>
       <c r="F30">
-        <v>-213.3255827067548</v>
+        <v>-215.8994347451933</v>
       </c>
       <c r="G30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>l2_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>0.8771163692884485</v>
-      </c>
-      <c r="E31">
-        <v>-188.1220575076477</v>
-      </c>
-      <c r="F31">
-        <v>-192.3517768592431</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>argentina_2018_dummy</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>0.9152478590682325</v>
-      </c>
-      <c r="E32">
-        <v>-192.3517768592431</v>
-      </c>
-      <c r="F32">
-        <v>-196.5991409669552</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>3</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>l3_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>0.6779658854976038</v>
-      </c>
-      <c r="E33">
-        <v>-196.5991409669552</v>
-      </c>
-      <c r="F33">
-        <v>-200.6330061905594</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>4</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>l3_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>0.5123934070021352</v>
-      </c>
-      <c r="E34">
-        <v>-200.6330061905594</v>
-      </c>
-      <c r="F34">
-        <v>-204.3366025602405</v>
-      </c>
-      <c r="G34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>5</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>l2_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>0.3813353210222058</v>
-      </c>
-      <c r="E35">
-        <v>-204.3366025602405</v>
-      </c>
-      <c r="F35">
-        <v>-207.6189020879323</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>6</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>covid_dummy</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>0.3518609645469802</v>
-      </c>
-      <c r="E36">
-        <v>-207.6189020879323</v>
-      </c>
-      <c r="F36">
-        <v>-210.7924663088147</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>7</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>l4_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>0.2619346556913756</v>
-      </c>
-      <c r="E37">
-        <v>-210.7924663088147</v>
-      </c>
-      <c r="F37">
-        <v>-213.5012520320983</v>
-      </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>global_crisis_dummy</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>0.1141610429150342</v>
-      </c>
-      <c r="E38">
-        <v>-213.5012520320983</v>
-      </c>
-      <c r="F38">
-        <v>-214.7352227707529</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>9</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>l2_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>0.1070814546819217</v>
-      </c>
-      <c r="E39">
-        <v>-214.7352227707529</v>
-      </c>
-      <c r="F39">
-        <v>-215.8994347451933</v>
-      </c>
-      <c r="G39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1950,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2115,33 +1873,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>elasticidad ingreso socios corto plazo - exportaciones</t>
+          <t>velocidad de ajuste ECM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios</t>
+          <t>l1_resid_imports_eg</t>
         </is>
       </c>
       <c r="E4">
-        <v>-0.2454196557573544</v>
+        <v>-0.3289306816518565</v>
       </c>
       <c r="F4">
-        <v>0.5377195459536575</v>
+        <v>3.707512354853029E-08</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2150,218 +1908,14 @@
         </is>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>revisar signo</t>
+          <t>consistente</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>Un aumento del PIB de socios comerciales deberia elevar la demanda externa de exportaciones argentinas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>exports_ecm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>exports</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>elasticidad tipo de cambio corto plazo - exportaciones</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>0.02089762196806905</v>
-      </c>
-      <c r="F5">
-        <v>0.9117768420638048</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>depende de la convencion del ITCRM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>requiere interpretar definicion</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>La interpretacion del signo requiere confirmar si un aumento del ITCRM implica depreciacion real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>exports_ecm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>exports</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>efecto commodity corto plazo - exportaciones</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>d_ln_commodity_price_index</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>0.1372167650417404</v>
-      </c>
-      <c r="F6">
-        <v>0.06092570487593698</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>consistente</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Un aumento de precios de commodities podria elevar el valor real/exportable asociado al sector externo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>exports_ecm</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>exports</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>velocidad de ajuste ECM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>l1_resid_exports_eg</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>-0.3296877998473486</v>
-      </c>
-      <c r="F7">
-        <v>0.01546877443348586</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>consistente</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>corrige aproximadamente 33% del desequilibrio por trimestre</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>velocidad de ajuste ECM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>l1_resid_imports_eg</t>
-        </is>
-      </c>
-      <c r="E8">
-        <v>-0.3289306816518565</v>
-      </c>
-      <c r="F8">
-        <v>3.707512354853029E-08</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>consistente</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>corrige aproximadamente 32.9% del desequilibrio por trimestre</t>
         </is>
@@ -2628,23 +2182,9 @@
           <t>Mayor actividad de socios comerciales aumenta la demanda externa.</t>
         </is>
       </c>
-      <c r="H5">
-        <v>-0.2454196557573544</v>
-      </c>
-      <c r="I5">
-        <v>0.5377195459536575</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>revisar signo</t>
+          <t>no estimado en especificacion final</t>
         </is>
       </c>
     </row>
@@ -2684,23 +2224,9 @@
           <t>Se asume convencion BCRA: aumento del ITCRM = depreciacion real multilateral.</t>
         </is>
       </c>
-      <c r="H6">
-        <v>0.02089762196806905</v>
-      </c>
-      <c r="I6">
-        <v>0.9117768420638048</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>consistente</t>
+          <t>no estimado en especificacion final</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2261,9 @@
           <t>Mayores precios de commodities pueden favorecer exportaciones asociadas.</t>
         </is>
       </c>
-      <c r="H7">
-        <v>0.1372167650417404</v>
-      </c>
-      <c r="I7">
-        <v>0.06092570487593698</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>positivo</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>consistente</t>
+          <t>no estimado en especificacion final</t>
         </is>
       </c>
     </row>
@@ -2786,23 +2298,9 @@
           <t>El ECM debe corregir desvios hacia el equilibrio de largo plazo.</t>
         </is>
       </c>
-      <c r="H8">
-        <v>-0.3296877998473486</v>
-      </c>
-      <c r="I8">
-        <v>0.01546877443348586</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>consistente</t>
+          <t>no estimado en especificacion final</t>
         </is>
       </c>
     </row>
@@ -2813,28 +2311,28 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model_key</t>
+          <t>source</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>trade_flow</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>model_label</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>term</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -2844,165 +2342,398 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>nw_std_error</t>
+          <t>reference_period</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>t_statistic</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>note</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>expected_sign</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>adjustment_speed</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>adjustment_percent_per_quarter</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dynamic_stability</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>adjustment_interpretation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>Este trabajo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>largo plazo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>l1_resid_exports_eg</t>
+          <t>ln_gdp_real</t>
         </is>
       </c>
       <c r="E2">
-        <v>-0.3296877998473486</v>
-      </c>
-      <c r="F2">
-        <v>0.1322791055847734</v>
-      </c>
-      <c r="G2">
-        <v>-2.492364900638539</v>
-      </c>
-      <c r="H2">
-        <v>0.01546877443348586</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="K2">
-        <v>0.3296877998473486</v>
-      </c>
-      <c r="L2">
-        <v>32.96877998473486</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>estable: convergencia gradual</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>corrige aproximadamente 33% del desequilibrio por trimestre</t>
+        <v>1.518408430994575</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>coeficiente de la ecuacion de cointegracion Engle-Granger</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Este trabajo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>largo plazo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>imports</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ln_itcrm</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>-0.3991932036902151</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>coeficiente de la ecuacion de cointegracion Engle-Granger</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Este trabajo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>largo plazo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>exports</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ln_pib_socios</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0.7203209712546355</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>coeficiente de la ecuacion de cointegracion Engle-Granger</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Este trabajo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>largo plazo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>exports</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ln_itcrm</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.1593885399165426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>coeficiente de la ecuacion de cointegracion Engle-Granger</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Este trabajo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>corto plazo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>imports</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>d_ln_gdp_real</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>1.41976235359121</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Un aumento del PIB real argentino deberia elevar la demanda de importaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Este trabajo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>corto plazo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>imports</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>d_ln_itcrm</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>-0.1067426584371333</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2004 Q1-2022 Q4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>La interpretacion del signo requiere confirmar si un aumento del ITCRM implica depreciacion real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Berrettoni y Castresana (2008)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Completar manualmente desde el paper antes de cerrar el informe; la consigna pide comparar resultados con la literatura sugerida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bus y Nicolini-Llosa (2007)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Completar manualmente desde el paper antes de cerrar el informe; la consigna pide comparar resultados con la literatura sugerida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Zack y Sotelsek (2016)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Completar manualmente desde el paper antes de cerrar el informe; la consigna pide comparar resultados con la literatura sugerida.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model_key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>trade_flow</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model_label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>nw_std_error</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>t_statistic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>expected_sign</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>adjustment_speed</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>adjustment_percent_per_quarter</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dynamic_stability</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>adjustment_interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>imports_ecm</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>imports</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Importaciones - ECM</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>l1_resid_imports_eg</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E2">
         <v>-0.3289306816518565</v>
       </c>
-      <c r="F3">
+      <c r="F2">
         <v>0.05225029336132092</v>
       </c>
-      <c r="G3">
+      <c r="G2">
         <v>-6.295288705409498</v>
       </c>
-      <c r="H3">
+      <c r="H2">
         <v>3.707512354853029E-08</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Newey-West HAC, lag = 4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>negativo</t>
         </is>
       </c>
-      <c r="K3">
+      <c r="K2">
         <v>0.3289306816518565</v>
       </c>
-      <c r="L3">
+      <c r="L2">
         <v>32.89306816518565</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>estable: convergencia gradual</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>corrige aproximadamente 32.9% del desequilibrio por trimestre</t>
         </is>
@@ -3137,16 +2868,16 @@
         </is>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>evidencia por Engle-Granger</t>
+          <t>sin evidencia de cointegracion</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>estimar ECM con termino de correccion del error</t>
+          <t>estimar modelo en primeras diferencias sin ECM</t>
         </is>
       </c>
       <c r="J2">
@@ -3216,20 +2947,20 @@
         </is>
       </c>
       <c r="G3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>evidencia por Engle-Granger</t>
+          <t>sin evidencia de cointegracion</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>estimar ECM con termino de correccion del error</t>
+          <t>estimar modelo en primeras diferencias sin ECM</t>
         </is>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3240,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -3254,12 +2985,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + d_ln_commodity_price_index + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l1_d_ln_commodity_price_index + l2_d_ln_commodity_price_index + l3_d_ln_commodity_price_index + l1_resid_exports_eg + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
+          <t>d_ln_pib_socios + d_ln_itcrm + d_ln_commodity_price_index + l1_d_ln_exports_real + l1_d_ln_pib_socios + l1_d_ln_itcrm + l1_d_ln_commodity_price_index + l1_resid_exports_eg + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>modelo ECM con termino de correccion del error rezagado</t>
+          <t>ECM no estimado porque la seccion 10 no encontro cointegracion</t>
         </is>
       </c>
     </row>
@@ -3757,20 +3488,8 @@
       <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11">
-        <v>71</v>
-      </c>
-      <c r="E11">
-        <v>-123.2481369025088</v>
-      </c>
-      <c r="F11">
-        <v>-93.83329850097167</v>
-      </c>
-      <c r="G11">
-        <v>-114.4505839038295</v>
-      </c>
       <c r="H11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3817,20 +3536,8 @@
       <c r="C13">
         <v>2</v>
       </c>
-      <c r="D13">
-        <v>71</v>
-      </c>
-      <c r="E13">
-        <v>-119.8912677942369</v>
-      </c>
-      <c r="F13">
-        <v>-81.42570988453457</v>
-      </c>
-      <c r="G13">
-        <v>-107.4945304626646</v>
-      </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3877,20 +3584,8 @@
       <c r="C15">
         <v>3</v>
       </c>
-      <c r="D15">
-        <v>71</v>
-      </c>
-      <c r="E15">
-        <v>-151.9887594469492</v>
-      </c>
-      <c r="F15">
-        <v>-104.4724820290816</v>
-      </c>
-      <c r="G15">
-        <v>-135.9928377824838</v>
-      </c>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3937,20 +3632,8 @@
       <c r="C17">
         <v>4</v>
       </c>
-      <c r="D17">
-        <v>71</v>
-      </c>
-      <c r="E17">
-        <v>-158.1904212309903</v>
-      </c>
-      <c r="F17">
-        <v>-101.6234243049574</v>
-      </c>
-      <c r="G17">
-        <v>-138.5953152336318</v>
-      </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4112,7 +3795,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>evidencia por Engle-Granger</t>
+          <t>sin evidencia de cointegracion</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -4143,52 +3826,16 @@
         </is>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + d_ln_commodity_price_index + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l3_d_ln_pib_socios + l3_d_ln_itcrm + l1_resid_exports_eg + covid_dummy</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>71</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2005Q2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2022Q4</t>
-        </is>
-      </c>
-      <c r="J3">
-        <v>0.6775189342091898</v>
-      </c>
-      <c r="K3">
-        <v>0.6237720899107215</v>
-      </c>
-      <c r="L3">
-        <v>0.07108989770627586</v>
-      </c>
-      <c r="M3">
-        <v>-161.883561029474</v>
-      </c>
-      <c r="N3">
-        <v>-134.7314025049782</v>
-      </c>
-      <c r="O3">
-        <v>-153.985804114018</v>
+        <v>1</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>evidencia por Engle-Granger</t>
+          <t>sin evidencia de cointegracion</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>modelo ECM con termino de correccion del error rezagado</t>
+          <t>ECM no estimado porque la seccion 10 no encontro cointegracion</t>
         </is>
       </c>
     </row>
@@ -4341,7 +3988,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4797,61 +4444,44 @@
           <t>Exportaciones - ECM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
-      </c>
-      <c r="E12">
-        <v>0.01147503070791181</v>
-      </c>
-      <c r="F12">
-        <v>0.009809762484964889</v>
-      </c>
-      <c r="G12">
-        <v>1.169756222487469</v>
-      </c>
-      <c r="H12">
-        <v>0.2467248803715966</v>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Newey-West HAC, lag = 4</t>
+          <t>ECM no estimado porque la seccion 10 no encontro cointegracion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="E13">
-        <v>-0.2454196557573544</v>
+        <v>-0.0006035068410535808</v>
       </c>
       <c r="F13">
-        <v>0.3959495762069779</v>
+        <v>0.005184360232617277</v>
       </c>
       <c r="G13">
-        <v>-0.6198255295746653</v>
+        <v>-0.1164091255188311</v>
       </c>
       <c r="H13">
-        <v>0.5377195459536575</v>
+        <v>0.9076928196545514</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -4862,35 +4492,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>d_ln_itcrm</t>
+          <t>d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E14">
-        <v>0.02089762196806905</v>
+        <v>1.433045511726144</v>
       </c>
       <c r="F14">
-        <v>0.1878168867928743</v>
+        <v>0.1144955763224451</v>
       </c>
       <c r="G14">
-        <v>0.1112659373973922</v>
+        <v>12.51616488387611</v>
       </c>
       <c r="H14">
-        <v>0.9117768420638048</v>
+        <v>7.376437761298554E-19</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -4901,35 +4531,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>d_ln_commodity_price_index</t>
+          <t>d_ln_itcrm</t>
         </is>
       </c>
       <c r="E15">
-        <v>0.1372167650417404</v>
+        <v>-0.1248908828620709</v>
       </c>
       <c r="F15">
-        <v>0.07184383961663189</v>
+        <v>0.08572232633098095</v>
       </c>
       <c r="G15">
-        <v>1.909930841307299</v>
+        <v>-1.456923630138745</v>
       </c>
       <c r="H15">
-        <v>0.06092570487593698</v>
+        <v>0.150026543684932</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4940,35 +4570,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>l1_d_ln_exports_real</t>
+          <t>l4_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E16">
-        <v>-0.5044302137793296</v>
+        <v>0.4006489420131162</v>
       </c>
       <c r="F16">
-        <v>0.0870124474386119</v>
+        <v>0.07063654656236276</v>
       </c>
       <c r="G16">
-        <v>-5.797219002892774</v>
+        <v>5.671978055430499</v>
       </c>
       <c r="H16">
-        <v>2.672626377036347E-07</v>
+        <v>3.655865459149129E-07</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -4979,35 +4609,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>l2_d_ln_exports_real</t>
+          <t>l1_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E17">
-        <v>-0.5839833954753028</v>
+        <v>0.5019871179949926</v>
       </c>
       <c r="F17">
-        <v>0.06767179875423118</v>
+        <v>0.08949705969943378</v>
       </c>
       <c r="G17">
-        <v>-8.629641981236521</v>
+        <v>5.608978883561787</v>
       </c>
       <c r="H17">
-        <v>4.164900922750199E-12</v>
+        <v>4.667151052239653E-07</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5018,35 +4648,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>l3_d_ln_exports_real</t>
+          <t>l4_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E18">
-        <v>-0.564459624691354</v>
+        <v>-1.17360982720589</v>
       </c>
       <c r="F18">
-        <v>0.0714660965853479</v>
+        <v>0.1151394163743081</v>
       </c>
       <c r="G18">
-        <v>-7.898285364127197</v>
+        <v>-10.19294577098244</v>
       </c>
       <c r="H18">
-        <v>7.307932830259292E-11</v>
+        <v>4.941565401117746E-15</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5057,35 +4687,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>l3_d_ln_pib_socios</t>
+          <t>l2_d_ln_itcrm</t>
         </is>
       </c>
       <c r="E19">
-        <v>1.700852195693394</v>
+        <v>-0.2705154813620385</v>
       </c>
       <c r="F19">
-        <v>0.61302250265505</v>
+        <v>0.08269011780812303</v>
       </c>
       <c r="G19">
-        <v>2.774534684007302</v>
+        <v>-3.27143664240208</v>
       </c>
       <c r="H19">
-        <v>0.007358661363647137</v>
+        <v>0.00172609009786258</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -5096,35 +4726,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>l3_d_ln_itcrm</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="E20">
-        <v>0.279399753816571</v>
+        <v>0.0009633073864088124</v>
       </c>
       <c r="F20">
-        <v>0.09876777033533353</v>
+        <v>0.004472510715389322</v>
       </c>
       <c r="G20">
-        <v>2.828855535241515</v>
+        <v>0.2153840309636818</v>
       </c>
       <c r="H20">
-        <v>0.006342786773764801</v>
+        <v>0.8301864494018921</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5135,35 +4765,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>l1_resid_exports_eg</t>
+          <t>d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E21">
-        <v>-0.3296877998473486</v>
+        <v>1.41976235359121</v>
       </c>
       <c r="F21">
-        <v>0.1322791055847734</v>
+        <v>0.08786840152792195</v>
       </c>
       <c r="G21">
-        <v>-2.492364900638539</v>
+        <v>16.15782612296699</v>
       </c>
       <c r="H21">
-        <v>0.01546877443348586</v>
+        <v>1.026482176599036E-23</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -5174,35 +4804,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>covid_dummy</t>
+          <t>d_ln_itcrm</t>
         </is>
       </c>
       <c r="E22">
-        <v>-0.1823196869595994</v>
+        <v>-0.1067426584371333</v>
       </c>
       <c r="F22">
-        <v>0.02232245264857397</v>
+        <v>0.05397965360386187</v>
       </c>
       <c r="G22">
-        <v>-8.167547259698033</v>
+        <v>-1.977460974842131</v>
       </c>
       <c r="H22">
-        <v>2.538658000413707E-11</v>
+        <v>0.05251295906584737</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -5213,7 +4843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5223,25 +4853,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>l1_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E23">
-        <v>-0.0006035068410535808</v>
+        <v>0.2193043988665623</v>
       </c>
       <c r="F23">
-        <v>0.005184360232617277</v>
+        <v>0.06023680352404853</v>
       </c>
       <c r="G23">
-        <v>-0.1164091255188311</v>
+        <v>3.640704453698455</v>
       </c>
       <c r="H23">
-        <v>0.9076928196545514</v>
+        <v>0.0005619467254554085</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -5252,7 +4882,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5262,25 +4892,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>d_ln_gdp_real</t>
+          <t>l4_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E24">
-        <v>1.433045511726144</v>
+        <v>0.4410252386054068</v>
       </c>
       <c r="F24">
-        <v>0.1144955763224451</v>
+        <v>0.0597069308385028</v>
       </c>
       <c r="G24">
-        <v>12.51616488387611</v>
+        <v>7.386499898953203</v>
       </c>
       <c r="H24">
-        <v>7.376437761298554E-19</v>
+        <v>5.011244408614724E-10</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5291,7 +4921,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5301,25 +4931,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>d_ln_itcrm</t>
+          <t>l1_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E25">
-        <v>-0.1248908828620709</v>
+        <v>0.2074125983737998</v>
       </c>
       <c r="F25">
-        <v>0.08572232633098095</v>
+        <v>0.09447340081149878</v>
       </c>
       <c r="G25">
-        <v>-1.456923630138745</v>
+        <v>2.195460273391097</v>
       </c>
       <c r="H25">
-        <v>0.150026543684932</v>
+        <v>0.03194478101868216</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -5330,7 +4960,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5340,25 +4970,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>l4_d_ln_imports_real</t>
+          <t>l3_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E26">
-        <v>0.4006489420131162</v>
+        <v>0.1741089785344909</v>
       </c>
       <c r="F26">
-        <v>0.07063654656236276</v>
+        <v>0.05341193589920379</v>
       </c>
       <c r="G26">
-        <v>5.671978055430499</v>
+        <v>3.259739150122929</v>
       </c>
       <c r="H26">
-        <v>3.655865459149129E-07</v>
+        <v>0.001826041646920671</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -5369,7 +4999,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5379,25 +5009,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>l1_d_ln_gdp_real</t>
+          <t>l4_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E27">
-        <v>0.5019871179949926</v>
+        <v>-0.9721437802176205</v>
       </c>
       <c r="F27">
-        <v>0.08949705969943378</v>
+        <v>0.1152735880348147</v>
       </c>
       <c r="G27">
-        <v>5.608978883561787</v>
+        <v>-8.433360987462418</v>
       </c>
       <c r="H27">
-        <v>4.667151052239653E-07</v>
+        <v>7.927060772342014E-12</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -5408,7 +5038,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5418,25 +5048,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>l4_d_ln_gdp_real</t>
+          <t>l1_d_ln_itcrm</t>
         </is>
       </c>
       <c r="E28">
-        <v>-1.17360982720589</v>
+        <v>0.192230068427191</v>
       </c>
       <c r="F28">
-        <v>0.1151394163743081</v>
+        <v>0.07374765529180831</v>
       </c>
       <c r="G28">
-        <v>-10.19294577098244</v>
+        <v>2.606592272887398</v>
       </c>
       <c r="H28">
-        <v>4.941565401117746E-15</v>
+        <v>0.0114780482894096</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -5447,7 +5077,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5457,417 +5087,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>l2_d_ln_itcrm</t>
+          <t>l1_resid_imports_eg</t>
         </is>
       </c>
       <c r="E29">
-        <v>-0.2705154813620385</v>
+        <v>-0.3289306816518565</v>
       </c>
       <c r="F29">
-        <v>0.08269011780812303</v>
+        <v>0.05225029336132092</v>
       </c>
       <c r="G29">
-        <v>-3.27143664240208</v>
+        <v>-6.295288705409498</v>
       </c>
       <c r="H29">
-        <v>0.00172609009786258</v>
+        <v>3.707512354853029E-08</v>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>(Intercept)</t>
-        </is>
-      </c>
-      <c r="E30">
-        <v>0.0009633073864088124</v>
-      </c>
-      <c r="F30">
-        <v>0.004472510715389322</v>
-      </c>
-      <c r="G30">
-        <v>0.2153840309636818</v>
-      </c>
-      <c r="H30">
-        <v>0.8301864494018921</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E31">
-        <v>1.41976235359121</v>
-      </c>
-      <c r="F31">
-        <v>0.08786840152792195</v>
-      </c>
-      <c r="G31">
-        <v>16.15782612296699</v>
-      </c>
-      <c r="H31">
-        <v>1.026482176599036E-23</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E32">
-        <v>-0.1067426584371333</v>
-      </c>
-      <c r="F32">
-        <v>0.05397965360386187</v>
-      </c>
-      <c r="G32">
-        <v>-1.977460974842131</v>
-      </c>
-      <c r="H32">
-        <v>0.05251295906584737</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>l1_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="E33">
-        <v>0.2193043988665623</v>
-      </c>
-      <c r="F33">
-        <v>0.06023680352404853</v>
-      </c>
-      <c r="G33">
-        <v>3.640704453698455</v>
-      </c>
-      <c r="H33">
-        <v>0.0005619467254554085</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>l4_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="E34">
-        <v>0.4410252386054068</v>
-      </c>
-      <c r="F34">
-        <v>0.0597069308385028</v>
-      </c>
-      <c r="G34">
-        <v>7.386499898953203</v>
-      </c>
-      <c r="H34">
-        <v>5.011244408614724E-10</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>l1_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E35">
-        <v>0.2074125983737998</v>
-      </c>
-      <c r="F35">
-        <v>0.09447340081149878</v>
-      </c>
-      <c r="G35">
-        <v>2.195460273391097</v>
-      </c>
-      <c r="H35">
-        <v>0.03194478101868216</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>l3_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E36">
-        <v>0.1741089785344909</v>
-      </c>
-      <c r="F36">
-        <v>0.05341193589920379</v>
-      </c>
-      <c r="G36">
-        <v>3.259739150122929</v>
-      </c>
-      <c r="H36">
-        <v>0.001826041646920671</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>l4_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E37">
-        <v>-0.9721437802176205</v>
-      </c>
-      <c r="F37">
-        <v>0.1152735880348147</v>
-      </c>
-      <c r="G37">
-        <v>-8.433360987462418</v>
-      </c>
-      <c r="H37">
-        <v>7.927060772342014E-12</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>l1_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E38">
-        <v>0.192230068427191</v>
-      </c>
-      <c r="F38">
-        <v>0.07374765529180831</v>
-      </c>
-      <c r="G38">
-        <v>2.606592272887398</v>
-      </c>
-      <c r="H38">
-        <v>0.0114780482894096</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Newey-West HAC, lag = 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>l1_resid_imports_eg</t>
-        </is>
-      </c>
-      <c r="E39">
-        <v>-0.3289306816518565</v>
-      </c>
-      <c r="F39">
-        <v>0.05225029336132092</v>
-      </c>
-      <c r="G39">
-        <v>-6.295288705409498</v>
-      </c>
-      <c r="H39">
-        <v>3.707512354853029E-08</v>
-      </c>
-      <c r="I39" t="inlineStr">
         <is>
           <t>Newey-West HAC, lag = 4</t>
         </is>
@@ -5880,7 +5120,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6010,33 +5250,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D3">
-        <v>0.8881066849164436</v>
+        <v>0.1105463733663874</v>
       </c>
       <c r="E3">
-        <v>0.210634350170605</v>
+        <v>0.535991066053781</v>
       </c>
       <c r="F3">
-        <v>0.6622367556746986</v>
+        <v>0.1724643085827477</v>
       </c>
       <c r="G3">
-        <v>0.9560040278563603</v>
+        <v>0.2577772109866205</v>
       </c>
       <c r="H3">
-        <v>0.789427366893068</v>
+        <v>0.9454589346969281</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6067,7 +5307,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6077,23 +5317,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D4">
-        <v>0.1105463733663874</v>
+        <v>0.1414347456519745</v>
       </c>
       <c r="E4">
-        <v>0.535991066053781</v>
+        <v>0.846998319281811</v>
       </c>
       <c r="F4">
-        <v>0.1724643085827477</v>
+        <v>0.411018318616428</v>
       </c>
       <c r="G4">
-        <v>0.2577772109866205</v>
+        <v>0.2812534709451062</v>
       </c>
       <c r="H4">
-        <v>0.9454589346969281</v>
+        <v>0.4901623900409602</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -6116,63 +5356,6 @@
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>p-valores altos no rechazan el supuesto diagnostico correspondiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.1414347456519745</v>
-      </c>
-      <c r="E5">
-        <v>0.846998319281811</v>
-      </c>
-      <c r="F5">
-        <v>0.411018318616428</v>
-      </c>
-      <c r="G5">
-        <v>0.2812534709451062</v>
-      </c>
-      <c r="H5">
-        <v>0.4901623900409602</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>sin evidencia al 5%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>p-valores altos no rechazan el supuesto diagnostico correspondiente</t>
         </is>
@@ -6185,7 +5368,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6493,26 +5676,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios</t>
+          <t>d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E11">
-        <v>1.604701705722772</v>
+        <v>3.877857967184955</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6523,17 +5706,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6542,7 +5725,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.178428557578574</v>
+        <v>1.037604122572211</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6553,26 +5736,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>d_ln_commodity_price_index</t>
+          <t>l4_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E13">
-        <v>1.695751708934252</v>
+        <v>1.758047348013267</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6583,26 +5766,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>l1_d_ln_exports_real</t>
+          <t>l1_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E14">
-        <v>3.561517772257002</v>
+        <v>1.85689338252994</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -6613,56 +5796,56 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>l2_d_ln_exports_real</t>
+          <t>l4_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E15">
-        <v>2.46613265314639</v>
+        <v>5.170065236029226</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>moderada</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_diff</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - primeras diferencias</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>l3_d_ln_exports_real</t>
+          <t>l2_d_ln_itcrm</t>
         </is>
       </c>
       <c r="E16">
-        <v>1.859676880977608</v>
+        <v>1.07328279969981</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -6673,26 +5856,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>l3_d_ln_pib_socios</t>
+          <t>d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E17">
-        <v>1.097298208456527</v>
+        <v>4.232076074986817</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -6703,26 +5886,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>l3_d_ln_itcrm</t>
+          <t>d_ln_itcrm</t>
         </is>
       </c>
       <c r="E18">
-        <v>1.172324408030625</v>
+        <v>1.16219674223838</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -6733,26 +5916,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>l1_resid_exports_eg</t>
+          <t>l1_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E19">
-        <v>2.859719677644831</v>
+        <v>1.415099653833543</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -6763,26 +5946,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exports_ecm</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>imports</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Exportaciones - ECM</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>covid_dummy</t>
+          <t>l4_d_ln_imports_real</t>
         </is>
       </c>
       <c r="E20">
-        <v>1.147067121671182</v>
+        <v>1.891158241308936</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -6793,7 +5976,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6803,16 +5986,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>d_ln_gdp_real</t>
+          <t>l1_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E21">
-        <v>3.877857967184955</v>
+        <v>2.700981473065423</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -6823,7 +6006,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6833,16 +6016,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>d_ln_itcrm</t>
+          <t>l3_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E22">
-        <v>1.037604122572211</v>
+        <v>1.857415977170139</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -6853,7 +6036,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6863,27 +6046,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>l4_d_ln_imports_real</t>
+          <t>l4_d_ln_gdp_real</t>
         </is>
       </c>
       <c r="E23">
-        <v>1.758047348013267</v>
+        <v>5.339974014417702</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>moderada</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6893,16 +6076,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>l1_d_ln_gdp_real</t>
+          <t>l1_d_ln_itcrm</t>
         </is>
       </c>
       <c r="E24">
-        <v>1.85689338252994</v>
+        <v>1.307001260558496</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -6913,7 +6096,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>imports_diff</t>
+          <t>imports_ecm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6923,318 +6106,18 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Importaciones - primeras diferencias</t>
+          <t>Importaciones - ECM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>l4_d_ln_gdp_real</t>
+          <t>l1_resid_imports_eg</t>
         </is>
       </c>
       <c r="E25">
-        <v>5.170065236029226</v>
+        <v>2.336965528711828</v>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>imports_diff</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Importaciones - primeras diferencias</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>l2_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E26">
-        <v>1.07328279969981</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E27">
-        <v>4.232076074986817</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E28">
-        <v>1.16219674223838</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>l1_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="E29">
-        <v>1.415099653833543</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>l4_d_ln_imports_real</t>
-        </is>
-      </c>
-      <c r="E30">
-        <v>1.891158241308936</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>l1_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E31">
-        <v>2.700981473065423</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>l3_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E32">
-        <v>1.857415977170139</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>l4_d_ln_gdp_real</t>
-        </is>
-      </c>
-      <c r="E33">
-        <v>5.339974014417702</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>moderada</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>l1_d_ln_itcrm</t>
-        </is>
-      </c>
-      <c r="E34">
-        <v>1.307001260558496</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>imports_ecm</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>imports</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Importaciones - ECM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>l1_resid_imports_eg</t>
-        </is>
-      </c>
-      <c r="E35">
-        <v>2.336965528711828</v>
-      </c>
-      <c r="F35" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
@@ -7327,7 +6210,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7485,17 +6368,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exports_ecm_with_commodities</t>
+          <t>exports_diff_lagged_commodity_only</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>with_commodities</t>
+          <t>lagged_commodity_only</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ecm</t>
+          <t>diff</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -7513,32 +6396,26 @@
         <v>71</v>
       </c>
       <c r="H3">
-        <v>0.712309082822154</v>
+        <v>0.6702304071090148</v>
       </c>
       <c r="I3">
-        <v>0.6051301136774663</v>
+        <v>0.5644552546722837</v>
       </c>
       <c r="J3">
-        <v>0.0728298459961641</v>
+        <v>0.07648896308847389</v>
       </c>
       <c r="K3">
-        <v>-151.9887594469492</v>
+        <v>-146.2967264040782</v>
       </c>
       <c r="L3">
-        <v>-104.4724820290816</v>
+        <v>-103.3058087402932</v>
       </c>
       <c r="M3">
-        <v>-135.9928377824838</v>
-      </c>
-      <c r="N3">
-        <v>0.178913088110097</v>
-      </c>
-      <c r="O3">
-        <v>0.01967129775977919</v>
+        <v>-132.1003969060593</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + d_ln_commodity_price_index + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l1_d_ln_commodity_price_index + l2_d_ln_commodity_price_index + l3_d_ln_commodity_price_index + l1_resid_exports_eg + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
+          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l1_d_ln_commodity_price_index + l2_d_ln_commodity_price_index + l3_d_ln_commodity_price_index + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -7550,12 +6427,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exports_diff_lagged_commodity_only</t>
+          <t>exports_diff_without_commodities</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lagged_commodity_only</t>
+          <t>without_commodities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7564,7 +6441,7 @@
         </is>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -7578,206 +6455,29 @@
         <v>71</v>
       </c>
       <c r="H4">
-        <v>0.6702304071090148</v>
+        <v>0.6603339109058191</v>
       </c>
       <c r="I4">
-        <v>0.5644552546722837</v>
+        <v>0.5754173886322738</v>
       </c>
       <c r="J4">
-        <v>0.07648896308847389</v>
+        <v>0.07552026168424643</v>
       </c>
       <c r="K4">
-        <v>-146.2967264040782</v>
+        <v>-150.1973389840999</v>
       </c>
       <c r="L4">
-        <v>-103.3058087402932</v>
+        <v>-113.9944609514389</v>
       </c>
       <c r="M4">
-        <v>-132.1003969060593</v>
+        <v>-138.7003977357509</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l1_d_ln_commodity_price_index + l2_d_ln_commodity_price_index + l3_d_ln_commodity_price_index + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
+          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
-        <is>
-          <t>Sensibilidad de exportaciones con y sin commodity price index; comparar AIC/BIC/HQ y significancia del termino de commodities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>exports_ecm_lagged_commodity_only</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>lagged_commodity_only</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ecm</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>71</v>
-      </c>
-      <c r="H5">
-        <v>0.7623724140306529</v>
-      </c>
-      <c r="I5">
-        <v>0.6534597704613689</v>
-      </c>
-      <c r="J5">
-        <v>0.06822746159109309</v>
-      </c>
-      <c r="K5">
-        <v>-159.5626826030154</v>
-      </c>
-      <c r="L5">
-        <v>-105.2583655540238</v>
-      </c>
-      <c r="M5">
-        <v>-140.8673726888802</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l4_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l4_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l4_d_ln_itcrm + l1_d_ln_commodity_price_index + l2_d_ln_commodity_price_index + l3_d_ln_commodity_price_index + l4_d_ln_commodity_price_index + l1_resid_exports_eg + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sensibilidad de exportaciones con y sin commodity price index; comparar AIC/BIC/HQ y significancia del termino de commodities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>exports_diff_without_commodities</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>without_commodities</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>diff</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>71</v>
-      </c>
-      <c r="H6">
-        <v>0.6603339109058191</v>
-      </c>
-      <c r="I6">
-        <v>0.5754173886322738</v>
-      </c>
-      <c r="J6">
-        <v>0.07552026168424643</v>
-      </c>
-      <c r="K6">
-        <v>-150.1973389840999</v>
-      </c>
-      <c r="L6">
-        <v>-113.9944609514389</v>
-      </c>
-      <c r="M6">
-        <v>-138.7003977357509</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Sensibilidad de exportaciones con y sin commodity price index; comparar AIC/BIC/HQ y significancia del termino de commodities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>exports_ecm_without_commodities</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>without_commodities</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ecm</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>71</v>
-      </c>
-      <c r="H7">
-        <v>0.7554698926943982</v>
-      </c>
-      <c r="I7">
-        <v>0.6708248555501515</v>
-      </c>
-      <c r="J7">
-        <v>0.06649605820113628</v>
-      </c>
-      <c r="K7">
-        <v>-165.5296859068122</v>
-      </c>
-      <c r="L7">
-        <v>-120.2760883659859</v>
-      </c>
-      <c r="M7">
-        <v>-150.43356032557</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>d_ln_pib_socios + d_ln_itcrm + l1_d_ln_exports_real + l2_d_ln_exports_real + l3_d_ln_exports_real + l4_d_ln_exports_real + l1_d_ln_pib_socios + l2_d_ln_pib_socios + l3_d_ln_pib_socios + l4_d_ln_pib_socios + l1_d_ln_itcrm + l2_d_ln_itcrm + l3_d_ln_itcrm + l4_d_ln_itcrm + l1_resid_exports_eg + global_crisis_dummy + argentina_2018_dummy + covid_dummy</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
         <is>
           <t>Sensibilidad de exportaciones con y sin commodity price index; comparar AIC/BIC/HQ y significancia del termino de commodities.</t>
         </is>
